--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AI35" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ35" s="5" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ44" s="5" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AI48" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ48" s="5" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI49" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ49" s="5" t="n">
@@ -6453,11 +6453,11 @@
       <c r="B50" s="3" t="n"/>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="5" t="n">
-        <v>561419093</v>
+        <v>561204793</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>HF509339752</t>
+          <t>HF508997880</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Aetna Medicare PPO</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Aetna Medicare PPO</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K50" s="4" t="n"/>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O50" s="6" t="inlineStr">
         <is>
-          <t>AETNA</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P50" s="6" t="n"/>
@@ -6510,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U50" s="8" t="n">
         <v>0</v>
@@ -6520,14 +6520,14 @@
       </c>
       <c r="W50" s="6" t="n"/>
       <c r="X50" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y50" s="5" t="n">
         <v>66</v>
       </c>
       <c r="Z50" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA50" s="6" t="n"/>
@@ -6536,12 +6536,12 @@
       <c r="AD50" s="5" t="n"/>
       <c r="AE50" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF50" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG50" s="6" t="inlineStr">
@@ -6556,11 +6556,11 @@
       </c>
       <c r="AI50" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
         </is>
       </c>
       <c r="AJ50" s="5" t="n">
-        <v>861</v>
+        <v>810</v>
       </c>
     </row>
     <row r="51">
@@ -6568,11 +6568,11 @@
       <c r="B51" s="3" t="n"/>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="5" t="n">
-        <v>561419093</v>
+        <v>561204793</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>HF509339752</t>
+          <t>HF508997880</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Aetna Medicare PPO</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Aetna Medicare PPO</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K51" s="4" t="n"/>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>AETNA</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P51" s="6" t="n"/>
@@ -6625,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="T51" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U51" s="8" t="n">
         <v>0</v>
@@ -6635,14 +6635,14 @@
       </c>
       <c r="W51" s="6" t="n"/>
       <c r="X51" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y51" s="5" t="n">
         <v>66</v>
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA51" s="6" t="n"/>
@@ -6651,12 +6651,12 @@
       <c r="AD51" s="5" t="n"/>
       <c r="AE51" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF51" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG51" s="6" t="inlineStr">
@@ -6671,11 +6671,11 @@
       </c>
       <c r="AI51" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
         </is>
       </c>
       <c r="AJ51" s="5" t="n">
-        <v>862</v>
+        <v>811</v>
       </c>
     </row>
     <row r="52">
@@ -6683,26 +6683,26 @@
       <c r="B52" s="3" t="n"/>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="5" t="n">
-        <v>561399071</v>
+        <v>561419093</v>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>HF462418285</t>
+          <t>HF509339752</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Aetna Medicare PPO</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Aetna Medicare PPO</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K52" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
         <v/>
       </c>
       <c r="M52" s="7" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U52" s="8" t="n">
         <v>0</v>
@@ -6750,14 +6750,14 @@
       </c>
       <c r="W52" s="6" t="n"/>
       <c r="X52" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y52" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z52" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA52" s="6" t="n"/>
@@ -6766,12 +6766,12 @@
       <c r="AD52" s="5" t="n"/>
       <c r="AE52" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF52" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG52" s="6" t="inlineStr">
@@ -6786,11 +6786,11 @@
       </c>
       <c r="AI52" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ52" s="5" t="n">
-        <v>1056</v>
+        <v>861</v>
       </c>
     </row>
     <row r="53">
@@ -6798,26 +6798,26 @@
       <c r="B53" s="3" t="n"/>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="5" t="n">
-        <v>561399071</v>
+        <v>561419093</v>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>HF462418285</t>
+          <t>HF509339752</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Aetna Medicare PPO</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Aetna Medicare PPO</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K53" s="4" t="n"/>
@@ -6836,7 +6836,7 @@
         <v/>
       </c>
       <c r="M53" s="7" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U53" s="8" t="n">
         <v>0</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="W53" s="6" t="n"/>
       <c r="X53" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y53" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA53" s="6" t="n"/>
@@ -6881,12 +6881,12 @@
       <c r="AD53" s="5" t="n"/>
       <c r="AE53" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF53" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG53" s="6" t="inlineStr">
@@ -6901,11 +6901,11 @@
       </c>
       <c r="AI53" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ53" s="5" t="n">
-        <v>1057</v>
+        <v>862</v>
       </c>
     </row>
     <row r="54">
@@ -6913,16 +6913,16 @@
       <c r="B54" s="3" t="n"/>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="5" t="n">
-        <v>561595295</v>
+        <v>561399071</v>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>HF507546981</t>
+          <t>HF462418285</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="M54" s="7" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
@@ -6983,11 +6983,11 @@
         <v>396.27</v>
       </c>
       <c r="Y54" s="5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z54" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA54" s="6" t="n"/>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AF54" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG54" s="6" t="inlineStr">
@@ -7016,11 +7016,11 @@
       </c>
       <c r="AI54" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ54" s="5" t="n">
-        <v>1027</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="55">
@@ -7028,16 +7028,16 @@
       <c r="B55" s="3" t="n"/>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="5" t="n">
-        <v>561595295</v>
+        <v>561399071</v>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>HF507546981</t>
+          <t>HF462418285</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K55" s="4" t="n"/>
@@ -7066,7 +7066,7 @@
         <v/>
       </c>
       <c r="M55" s="7" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="U55" s="8" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="W55" s="6" t="n"/>
       <c r="X55" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="Y55" s="5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA55" s="6" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AF55" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG55" s="6" t="inlineStr">
@@ -7131,11 +7131,11 @@
       </c>
       <c r="AI55" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ55" s="5" t="n">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="56">
@@ -7143,36 +7143,36 @@
       <c r="B56" s="3" t="n"/>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="5" t="n">
-        <v>562134294</v>
+        <v>561595295</v>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>HF529910506</t>
+          <t>HF507546981</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K56" s="4" t="n"/>
@@ -7181,7 +7181,7 @@
         <v/>
       </c>
       <c r="M56" s="7" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AETNA</t>
         </is>
       </c>
       <c r="P56" s="6" t="n"/>
@@ -7200,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U56" s="8" t="n">
         <v>0</v>
@@ -7210,27 +7210,23 @@
       </c>
       <c r="W56" s="6" t="n"/>
       <c r="X56" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y56" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
-        </is>
-      </c>
-      <c r="AA56" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F4320</t>
+        </is>
+      </c>
+      <c r="AA56" s="6" t="n"/>
       <c r="AB56" s="6" t="n"/>
       <c r="AC56" s="6" t="n"/>
       <c r="AD56" s="5" t="n"/>
       <c r="AE56" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF56" s="6" t="inlineStr">
@@ -7248,9 +7244,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI56" s="9" t="n"/>
+      <c r="AI56" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 120 days per contract.</t>
+        </is>
+      </c>
       <c r="AJ56" s="5" t="n">
-        <v>238</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="57">
@@ -7258,36 +7258,36 @@
       <c r="B57" s="3" t="n"/>
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="5" t="n">
-        <v>562134294</v>
+        <v>561595295</v>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>HF529910506</t>
+          <t>HF507546981</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K57" s="4" t="n"/>
@@ -7296,7 +7296,7 @@
         <v/>
       </c>
       <c r="M57" s="7" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
@@ -7305,17 +7305,17 @@
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AETNA</t>
         </is>
       </c>
       <c r="P57" s="6" t="n"/>
       <c r="Q57" s="6" t="n"/>
       <c r="R57" s="6" t="n"/>
       <c r="S57" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" s="8" t="n">
-        <v>792.54</v>
+        <v>1029.98</v>
       </c>
       <c r="U57" s="8" t="n">
         <v>0</v>
@@ -7325,27 +7325,23 @@
       </c>
       <c r="W57" s="6" t="n"/>
       <c r="X57" s="8" t="n">
-        <v>792.54</v>
+        <v>1029.98</v>
       </c>
       <c r="Y57" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z57" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
-        </is>
-      </c>
-      <c r="AA57" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F4320</t>
+        </is>
+      </c>
+      <c r="AA57" s="6" t="n"/>
       <c r="AB57" s="6" t="n"/>
       <c r="AC57" s="6" t="n"/>
       <c r="AD57" s="5" t="n"/>
       <c r="AE57" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF57" s="6" t="inlineStr">
@@ -7363,9 +7359,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI57" s="9" t="n"/>
+      <c r="AI57" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 120 days per contract.</t>
+        </is>
+      </c>
       <c r="AJ57" s="5" t="n">
-        <v>239</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="58">
@@ -7373,31 +7373,31 @@
       <c r="B58" s="3" t="n"/>
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="5" t="n">
-        <v>561951317</v>
+        <v>562134294</v>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>HF524119358</t>
+          <t>HF529910506</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -7411,7 +7411,7 @@
         <v/>
       </c>
       <c r="M58" s="7" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P58" s="6" t="n"/>
@@ -7443,25 +7443,29 @@
         <v>976.64</v>
       </c>
       <c r="Y58" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
-        </is>
-      </c>
-      <c r="AA58" s="6" t="n"/>
+          <t>F330</t>
+        </is>
+      </c>
+      <c r="AA58" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB58" s="6" t="n"/>
       <c r="AC58" s="6" t="n"/>
       <c r="AD58" s="5" t="n"/>
       <c r="AE58" s="6" t="inlineStr">
         <is>
-          <t>KALLGREN, MARK</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF58" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG58" s="6" t="inlineStr">
@@ -7476,7 +7480,7 @@
       </c>
       <c r="AI58" s="9" t="n"/>
       <c r="AJ58" s="5" t="n">
-        <v>516</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59">
@@ -7484,31 +7488,31 @@
       <c r="B59" s="3" t="n"/>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="5" t="n">
-        <v>561951317</v>
+        <v>562134294</v>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>HF524119358</t>
+          <t>HF529910506</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
@@ -7522,7 +7526,7 @@
         <v/>
       </c>
       <c r="M59" s="7" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
@@ -7531,17 +7535,17 @@
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>AMBETTER</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P59" s="6" t="n"/>
       <c r="Q59" s="6" t="n"/>
       <c r="R59" s="6" t="n"/>
       <c r="S59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T59" s="8" t="n">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="U59" s="8" t="n">
         <v>0</v>
@@ -7551,28 +7555,32 @@
       </c>
       <c r="W59" s="6" t="n"/>
       <c r="X59" s="8" t="n">
-        <v>396.27</v>
+        <v>792.54</v>
       </c>
       <c r="Y59" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
-        </is>
-      </c>
-      <c r="AA59" s="6" t="n"/>
+          <t>F330</t>
+        </is>
+      </c>
+      <c r="AA59" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB59" s="6" t="n"/>
       <c r="AC59" s="6" t="n"/>
       <c r="AD59" s="5" t="n"/>
       <c r="AE59" s="6" t="inlineStr">
         <is>
-          <t>KALLGREN, MARK</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF59" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG59" s="6" t="inlineStr">
@@ -7587,7 +7595,7 @@
       </c>
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="5" t="n">
-        <v>517</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60">
@@ -7595,11 +7603,11 @@
       <c r="B60" s="3" t="n"/>
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="5" t="n">
-        <v>561962926</v>
+        <v>561951317</v>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>HF545220191</t>
+          <t>HF524119358</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -7609,12 +7617,12 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -7624,7 +7632,7 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K60" s="4" t="n"/>
@@ -7642,7 +7650,7 @@
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="P60" s="6" t="n"/>
@@ -7652,7 +7660,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="U60" s="8" t="n">
         <v>0</v>
@@ -7662,14 +7670,14 @@
       </c>
       <c r="W60" s="6" t="n"/>
       <c r="X60" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="Y60" s="5" t="n">
         <v>59</v>
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA60" s="6" t="n"/>
@@ -7678,7 +7686,7 @@
       <c r="AD60" s="5" t="n"/>
       <c r="AE60" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>KALLGREN, MARK</t>
         </is>
       </c>
       <c r="AF60" s="6" t="inlineStr">
@@ -7698,7 +7706,7 @@
       </c>
       <c r="AI60" s="9" t="n"/>
       <c r="AJ60" s="5" t="n">
-        <v>998</v>
+        <v>516</v>
       </c>
     </row>
     <row r="61">
@@ -7706,11 +7714,11 @@
       <c r="B61" s="3" t="n"/>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="5" t="n">
-        <v>561962926</v>
+        <v>561951317</v>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>HF545220191</t>
+          <t>HF524119358</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -7720,12 +7728,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -7753,7 +7761,7 @@
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AMBETTER</t>
         </is>
       </c>
       <c r="P61" s="6" t="n"/>
@@ -7780,7 +7788,7 @@
       </c>
       <c r="Z61" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA61" s="6" t="n"/>
@@ -7789,7 +7797,7 @@
       <c r="AD61" s="5" t="n"/>
       <c r="AE61" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>KALLGREN, MARK</t>
         </is>
       </c>
       <c r="AF61" s="6" t="inlineStr">
@@ -7809,7 +7817,7 @@
       </c>
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="5" t="n">
-        <v>1002</v>
+        <v>517</v>
       </c>
     </row>
     <row r="62">
@@ -7817,16 +7825,16 @@
       <c r="B62" s="3" t="n"/>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="5" t="n">
-        <v>562066397</v>
+        <v>561962926</v>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>HF534791010</t>
+          <t>HF545220191</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -7855,7 +7863,7 @@
         <v/>
       </c>
       <c r="M62" s="7" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
@@ -7887,11 +7895,11 @@
         <v>1029.98</v>
       </c>
       <c r="Y62" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA62" s="6" t="n"/>
@@ -7900,12 +7908,12 @@
       <c r="AD62" s="5" t="n"/>
       <c r="AE62" s="6" t="inlineStr">
         <is>
-          <t>CURRIE, DAVID</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF62" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Avondale</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG62" s="6" t="inlineStr">
@@ -7920,7 +7928,7 @@
       </c>
       <c r="AI62" s="9" t="n"/>
       <c r="AJ62" s="5" t="n">
-        <v>847</v>
+        <v>998</v>
       </c>
     </row>
     <row r="63">
@@ -7928,16 +7936,16 @@
       <c r="B63" s="3" t="n"/>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="5" t="n">
-        <v>562066397</v>
+        <v>561962926</v>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>HF534791010</t>
+          <t>HF545220191</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -7966,7 +7974,7 @@
         <v/>
       </c>
       <c r="M63" s="7" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
@@ -7998,11 +8006,11 @@
         <v>396.27</v>
       </c>
       <c r="Y63" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA63" s="6" t="n"/>
@@ -8011,12 +8019,12 @@
       <c r="AD63" s="5" t="n"/>
       <c r="AE63" s="6" t="inlineStr">
         <is>
-          <t>CURRIE, DAVID</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF63" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Avondale</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG63" s="6" t="inlineStr">
@@ -8031,7 +8039,7 @@
       </c>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="5" t="n">
-        <v>848</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="64">
@@ -8039,26 +8047,26 @@
       <c r="B64" s="3" t="n"/>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="5" t="n">
-        <v>562674720</v>
+        <v>562066397</v>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>HF521915818</t>
+          <t>HF534791010</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
@@ -8077,7 +8085,7 @@
         <v/>
       </c>
       <c r="M64" s="7" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
@@ -8086,7 +8094,7 @@
       </c>
       <c r="O64" s="6" t="inlineStr">
         <is>
-          <t>AETNA</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P64" s="6" t="n"/>
@@ -8109,11 +8117,11 @@
         <v>1029.98</v>
       </c>
       <c r="Y64" s="5" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Z64" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA64" s="6" t="n"/>
@@ -8122,12 +8130,12 @@
       <c r="AD64" s="5" t="n"/>
       <c r="AE64" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>CURRIE, DAVID</t>
         </is>
       </c>
       <c r="AF64" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - Avondale</t>
         </is>
       </c>
       <c r="AG64" s="6" t="inlineStr">
@@ -8140,13 +8148,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI64" s="9" t="inlineStr">
-        <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
-        </is>
-      </c>
+      <c r="AI64" s="9" t="n"/>
       <c r="AJ64" s="5" t="n">
-        <v>1041</v>
+        <v>847</v>
       </c>
     </row>
     <row r="65">
@@ -8154,26 +8158,26 @@
       <c r="B65" s="3" t="n"/>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="5" t="n">
-        <v>562674720</v>
+        <v>562066397</v>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>HF521915818</t>
+          <t>HF534791010</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Aetna Legacy</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -8192,7 +8196,7 @@
         <v/>
       </c>
       <c r="M65" s="7" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
@@ -8201,7 +8205,7 @@
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>AETNA</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P65" s="6" t="n"/>
@@ -8224,11 +8228,11 @@
         <v>396.27</v>
       </c>
       <c r="Y65" s="5" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA65" s="6" t="n"/>
@@ -8237,12 +8241,12 @@
       <c r="AD65" s="5" t="n"/>
       <c r="AE65" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>CURRIE, DAVID</t>
         </is>
       </c>
       <c r="AF65" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - Avondale</t>
         </is>
       </c>
       <c r="AG65" s="6" t="inlineStr">
@@ -8255,13 +8259,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI65" s="9" t="inlineStr">
-        <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
-        </is>
-      </c>
+      <c r="AI65" s="9" t="n"/>
       <c r="AJ65" s="5" t="n">
-        <v>1042</v>
+        <v>848</v>
       </c>
     </row>
     <row r="66">
@@ -8269,16 +8269,16 @@
       <c r="B66" s="3" t="n"/>
       <c r="C66" s="4" t="n"/>
       <c r="D66" s="5" t="n">
-        <v>562865132</v>
+        <v>562674720</v>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>HF332213773</t>
+          <t>HF521915818</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -8307,7 +8307,7 @@
         <v/>
       </c>
       <c r="M66" s="7" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
@@ -8339,11 +8339,11 @@
         <v>1029.98</v>
       </c>
       <c r="Y66" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA66" s="6" t="n"/>
@@ -8352,12 +8352,12 @@
       <c r="AD66" s="5" t="n"/>
       <c r="AE66" s="6" t="inlineStr">
         <is>
-          <t>MCMURDIE, TODD</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF66" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Surprise - Reems</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG66" s="6" t="inlineStr">
@@ -8372,11 +8372,11 @@
       </c>
       <c r="AI66" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ66" s="5" t="n">
-        <v>823</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="67">
@@ -8384,16 +8384,16 @@
       <c r="B67" s="3" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="5" t="n">
-        <v>562865132</v>
+        <v>562674720</v>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>HF332213773</t>
+          <t>HF521915818</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -8422,7 +8422,7 @@
         <v/>
       </c>
       <c r="M67" s="7" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
@@ -8454,11 +8454,11 @@
         <v>396.27</v>
       </c>
       <c r="Y67" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z67" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA67" s="6" t="n"/>
@@ -8467,12 +8467,12 @@
       <c r="AD67" s="5" t="n"/>
       <c r="AE67" s="6" t="inlineStr">
         <is>
-          <t>MCMURDIE, TODD</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF67" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Surprise - Reems</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG67" s="6" t="inlineStr">
@@ -8487,11 +8487,11 @@
       </c>
       <c r="AI67" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ67" s="5" t="n">
-        <v>830</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="68">
@@ -8499,26 +8499,26 @@
       <c r="B68" s="3" t="n"/>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="5" t="n">
-        <v>563308164</v>
+        <v>562865132</v>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>HF447955847</t>
+          <t>HF332213773</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
@@ -8537,7 +8537,7 @@
         <v/>
       </c>
       <c r="M68" s="7" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AETNA</t>
         </is>
       </c>
       <c r="P68" s="6" t="n"/>
@@ -8569,11 +8569,11 @@
         <v>1029.98</v>
       </c>
       <c r="Y68" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z68" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA68" s="6" t="n"/>
@@ -8582,12 +8582,12 @@
       <c r="AD68" s="5" t="n"/>
       <c r="AE68" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MCMURDIE, TODD</t>
         </is>
       </c>
       <c r="AF68" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Surprise - Reems</t>
         </is>
       </c>
       <c r="AG68" s="6" t="inlineStr">
@@ -8600,9 +8600,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI68" s="9" t="n"/>
+      <c r="AI68" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 120 days per contract.</t>
+        </is>
+      </c>
       <c r="AJ68" s="5" t="n">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="69">
@@ -8610,26 +8614,26 @@
       <c r="B69" s="3" t="n"/>
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="5" t="n">
-        <v>563308164</v>
+        <v>562865132</v>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>HF447955847</t>
+          <t>HF332213773</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Banner Health &amp; Aetna Health Insurance Company</t>
+          <t>Aetna Legacy</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -8648,7 +8652,7 @@
         <v/>
       </c>
       <c r="M69" s="7" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
@@ -8657,7 +8661,7 @@
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
+          <t>AETNA</t>
         </is>
       </c>
       <c r="P69" s="6" t="n"/>
@@ -8680,11 +8684,11 @@
         <v>396.27</v>
       </c>
       <c r="Y69" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z69" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA69" s="6" t="n"/>
@@ -8693,12 +8697,12 @@
       <c r="AD69" s="5" t="n"/>
       <c r="AE69" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MCMURDIE, TODD</t>
         </is>
       </c>
       <c r="AF69" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Surprise - Reems</t>
         </is>
       </c>
       <c r="AG69" s="6" t="inlineStr">
@@ -8711,9 +8715,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI69" s="9" t="n"/>
+      <c r="AI69" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 120 days per contract.</t>
+        </is>
+      </c>
       <c r="AJ69" s="5" t="n">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="70">
@@ -8721,26 +8729,26 @@
       <c r="B70" s="3" t="n"/>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="5" t="n">
-        <v>561204793</v>
+        <v>563308164</v>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>HF508997880</t>
+          <t>HF447955847</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -8750,7 +8758,7 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K70" s="4" t="n"/>
@@ -8759,16 +8767,16 @@
         <v/>
       </c>
       <c r="M70" s="7" t="n">
-        <v>46356</v>
+        <v>46315</v>
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P70" s="6" t="n"/>
@@ -8778,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U70" s="8" t="n">
         <v>0</v>
@@ -8788,14 +8796,14 @@
       </c>
       <c r="W70" s="6" t="n"/>
       <c r="X70" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y70" s="5" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="Z70" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA70" s="6" t="n"/>
@@ -8804,12 +8812,12 @@
       <c r="AD70" s="5" t="n"/>
       <c r="AE70" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF70" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG70" s="6" t="inlineStr">
@@ -8824,7 +8832,7 @@
       </c>
       <c r="AI70" s="9" t="n"/>
       <c r="AJ70" s="5" t="n">
-        <v>810</v>
+        <v>832</v>
       </c>
     </row>
     <row r="71">
@@ -8832,26 +8840,26 @@
       <c r="B71" s="3" t="n"/>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="5" t="n">
-        <v>561204793</v>
+        <v>563308164</v>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>HF508997880</t>
+          <t>HF447955847</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -8861,7 +8869,7 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K71" s="4" t="n"/>
@@ -8870,16 +8878,16 @@
         <v/>
       </c>
       <c r="M71" s="7" t="n">
-        <v>46356</v>
+        <v>46315</v>
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P71" s="6" t="n"/>
@@ -8889,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U71" s="8" t="n">
         <v>0</v>
@@ -8899,14 +8907,14 @@
       </c>
       <c r="W71" s="6" t="n"/>
       <c r="X71" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y71" s="5" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="Z71" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA71" s="6" t="n"/>
@@ -8915,12 +8923,12 @@
       <c r="AD71" s="5" t="n"/>
       <c r="AE71" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF71" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG71" s="6" t="inlineStr">
@@ -8935,7 +8943,7 @@
       </c>
       <c r="AI71" s="9" t="n"/>
       <c r="AJ71" s="5" t="n">
-        <v>811</v>
+        <v>833</v>
       </c>
     </row>
     <row r="72">
@@ -8981,11 +8989,11 @@
         <v/>
       </c>
       <c r="M72" s="7" t="n">
-        <v>46358</v>
+        <v>46355</v>
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
@@ -9050,7 +9058,7 @@
       </c>
       <c r="AI72" s="9" t="inlineStr">
         <is>
-          <t>Limit is stated in months, not days - counted as 6 calendar months.</t>
+          <t>Limit as stated: 6 months. The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ72" s="5" t="n">
@@ -9100,11 +9108,11 @@
         <v/>
       </c>
       <c r="M73" s="7" t="n">
-        <v>46358</v>
+        <v>46355</v>
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -9169,7 +9177,7 @@
       </c>
       <c r="AI73" s="9" t="inlineStr">
         <is>
-          <t>Limit is stated in months, not days - counted as 6 calendar months.</t>
+          <t>Limit as stated: 6 months. The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ73" s="5" t="n">
@@ -15334,7 +15342,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI128" s="9" t="n"/>
+      <c r="AI128" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ128" s="5" t="n">
         <v>607</v>
       </c>
@@ -15439,7 +15451,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI129" s="9" t="n"/>
+      <c r="AI129" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ129" s="5" t="n">
         <v>608</v>
       </c>
@@ -16888,7 +16904,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI142" s="9" t="n"/>
+      <c r="AI142" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ142" s="5" t="n">
         <v>915</v>
       </c>
@@ -17211,7 +17231,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI145" s="9" t="n"/>
+      <c r="AI145" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ145" s="5" t="n">
         <v>1017</v>
       </c>
@@ -17316,7 +17340,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI146" s="9" t="n"/>
+      <c r="AI146" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ146" s="5" t="n">
         <v>1031</v>
       </c>
@@ -17639,7 +17667,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI149" s="9" t="n"/>
+      <c r="AI149" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ149" s="5" t="n">
         <v>967</v>
       </c>
@@ -17744,7 +17776,11 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI150" s="9" t="n"/>
+      <c r="AI150" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ150" s="5" t="n">
         <v>968</v>
       </c>
@@ -18722,7 +18758,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI6" s="9" t="n"/>
+      <c r="AI6" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ6" s="5" t="n">
         <v>1058</v>
       </c>
@@ -18966,7 +19006,7 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
@@ -19210,7 +19250,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI10" s="9" t="n"/>
+      <c r="AI10" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ10" s="5" t="n">
         <v>871</v>
       </c>
@@ -19327,7 +19371,7 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
@@ -19811,7 +19855,7 @@
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
@@ -20176,7 +20220,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -20541,7 +20585,7 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
@@ -21021,7 +21065,7 @@
       </c>
       <c r="AI25" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
@@ -21384,7 +21428,7 @@
       </c>
       <c r="AI28" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
@@ -21511,26 +21555,26 @@
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="5" t="n">
-        <v>564103202</v>
+        <v>562134105</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>HF541974005</t>
+          <t>HF538936351</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>06/23/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>Health Choice Arizona</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -21540,7 +21584,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>A6010</t>
+          <t>L0457</t>
         </is>
       </c>
       <c r="K30" s="4" t="n"/>
@@ -21549,7 +21593,7 @@
         <v/>
       </c>
       <c r="M30" s="7" t="n">
-        <v>46376</v>
+        <v>46355</v>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
@@ -21558,21 +21602,21 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>MERCY CARE MEDICAID</t>
+          <t>HEALTH CHOICE MEDICAID</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>KX</t>
         </is>
       </c>
       <c r="Q30" s="6" t="n"/>
       <c r="R30" s="6" t="n"/>
       <c r="S30" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T30" s="8" t="n">
-        <v>5916.4</v>
+        <v>5320.49</v>
       </c>
       <c r="U30" s="8" t="n">
         <v>0</v>
@@ -21582,49 +21626,37 @@
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="X30" s="8" t="n">
-        <v>5916.4</v>
+        <v>5320.49</v>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="Z30" s="6" t="inlineStr">
         <is>
-          <t>G894</t>
-        </is>
-      </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>M4316</t>
-        </is>
-      </c>
-      <c r="AB30" s="6" t="inlineStr">
-        <is>
-          <t>M4726</t>
-        </is>
-      </c>
-      <c r="AC30" s="6" t="inlineStr">
-        <is>
-          <t>M48062</t>
-        </is>
-      </c>
+          <t>M47814</t>
+        </is>
+      </c>
+      <c r="AA30" s="6" t="n"/>
+      <c r="AB30" s="6" t="n"/>
+      <c r="AC30" s="6" t="n"/>
       <c r="AD30" s="5" t="n"/>
       <c r="AE30" s="6" t="inlineStr">
         <is>
-          <t>MCCUNNIFF, PETER</t>
+          <t>Arshad, Jawad</t>
         </is>
       </c>
       <c r="AF30" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Mesa</t>
         </is>
       </c>
       <c r="AG30" s="6" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>06/12/2026</t>
         </is>
       </c>
       <c r="AH30" s="6" t="inlineStr">
@@ -21632,9 +21664,13 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI30" s="9" t="n"/>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
+        </is>
+      </c>
       <c r="AJ30" s="5" t="n">
-        <v>829</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31">
@@ -21642,26 +21678,26 @@
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="5" t="n">
-        <v>562134105</v>
+        <v>564103202</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>HF538936351</t>
+          <t>HF541974005</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/23/2026</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Health Choice Arizona</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -21671,7 +21707,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>L0457</t>
+          <t>A6010</t>
         </is>
       </c>
       <c r="K31" s="4" t="n"/>
@@ -21680,30 +21716,30 @@
         <v/>
       </c>
       <c r="M31" s="7" t="n">
-        <v>46389</v>
+        <v>46376</v>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>HEALTH CHOICE MEDICAID</t>
+          <t>MERCY CARE MEDICAID</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>KX</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="Q31" s="6" t="n"/>
       <c r="R31" s="6" t="n"/>
       <c r="S31" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>5320.49</v>
+        <v>5916.4</v>
       </c>
       <c r="U31" s="8" t="n">
         <v>0</v>
@@ -21713,37 +21749,49 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="X31" s="8" t="n">
-        <v>5320.49</v>
+        <v>5916.4</v>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="Z31" s="6" t="inlineStr">
         <is>
-          <t>M47814</t>
-        </is>
-      </c>
-      <c r="AA31" s="6" t="n"/>
-      <c r="AB31" s="6" t="n"/>
-      <c r="AC31" s="6" t="n"/>
+          <t>G894</t>
+        </is>
+      </c>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>M4316</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="inlineStr">
+        <is>
+          <t>M4726</t>
+        </is>
+      </c>
+      <c r="AC31" s="6" t="inlineStr">
+        <is>
+          <t>M48062</t>
+        </is>
+      </c>
       <c r="AD31" s="5" t="n"/>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>Arshad, Jawad</t>
+          <t>MCCUNNIFF, PETER</t>
         </is>
       </c>
       <c r="AF31" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Mesa</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG31" s="6" t="inlineStr">
         <is>
-          <t>06/12/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="AH31" s="6" t="inlineStr">
@@ -21751,13 +21799,9 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI31" s="9" t="inlineStr">
-        <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
-        </is>
-      </c>
+      <c r="AI31" s="9" t="n"/>
       <c r="AJ31" s="5" t="n">
-        <v>397</v>
+        <v>829</v>
       </c>
     </row>
     <row r="32">
@@ -24334,7 +24378,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI52" s="9" t="n"/>
+      <c r="AI52" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ52" s="5" t="n">
         <v>916</v>
       </c>
@@ -24834,7 +24882,7 @@
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ2" s="5" t="n">
@@ -24965,7 +25013,7 @@
       </c>
       <c r="AI3" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="n">
@@ -25092,7 +25140,7 @@
       </c>
       <c r="AI4" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
@@ -25215,7 +25263,7 @@
       </c>
       <c r="AI5" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
@@ -25350,7 +25398,7 @@
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
@@ -25477,7 +25525,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -25608,7 +25656,7 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
@@ -27483,7 +27531,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI23" s="9" t="n"/>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ23" s="5" t="n">
         <v>293</v>
       </c>
@@ -27618,7 +27670,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI24" s="9" t="n"/>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ24" s="5" t="n">
         <v>294</v>
       </c>
@@ -27749,7 +27805,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI25" s="9" t="n"/>
+      <c r="AI25" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ25" s="5" t="n">
         <v>295</v>
       </c>
@@ -27876,7 +27936,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI26" s="9" t="n"/>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ26" s="5" t="n">
         <v>304</v>
       </c>
@@ -28007,7 +28071,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI27" s="9" t="n"/>
+      <c r="AI27" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ27" s="5" t="n">
         <v>305</v>
       </c>
@@ -29640,7 +29708,7 @@
       </c>
       <c r="AI40" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ40" s="5" t="n">
@@ -29767,7 +29835,7 @@
       </c>
       <c r="AI41" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ41" s="5" t="n">
@@ -29894,7 +29962,7 @@
       </c>
       <c r="AI42" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ42" s="5" t="n">
@@ -30017,7 +30085,7 @@
       </c>
       <c r="AI43" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ43" s="5" t="n">
@@ -30148,7 +30216,7 @@
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ44" s="5" t="n">
@@ -30624,7 +30692,7 @@
       </c>
       <c r="AI48" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ48" s="5" t="n">
@@ -30751,7 +30819,7 @@
       </c>
       <c r="AI49" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ49" s="5" t="n">
@@ -30874,7 +30942,7 @@
       </c>
       <c r="AI50" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ50" s="5" t="n">
@@ -31009,7 +31077,7 @@
       </c>
       <c r="AI51" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ51" s="5" t="n">
@@ -31136,7 +31204,7 @@
       </c>
       <c r="AI52" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ52" s="5" t="n">
@@ -31255,7 +31323,7 @@
       </c>
       <c r="AI53" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ53" s="5" t="n">
@@ -31370,7 +31438,7 @@
       </c>
       <c r="AI54" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ54" s="5" t="n">
@@ -31489,7 +31557,7 @@
       </c>
       <c r="AI55" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ55" s="5" t="n">
@@ -31957,7 +32025,7 @@
       </c>
       <c r="AI59" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ59" s="5" t="n">
@@ -32080,7 +32148,7 @@
       </c>
       <c r="AI60" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ60" s="5" t="n">
@@ -32211,7 +32279,7 @@
       </c>
       <c r="AI61" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ61" s="5" t="n">
@@ -32342,7 +32410,7 @@
       </c>
       <c r="AI62" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ62" s="5" t="n">
@@ -32469,7 +32537,7 @@
       </c>
       <c r="AI63" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ63" s="5" t="n">
@@ -32604,7 +32672,7 @@
       </c>
       <c r="AI64" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ64" s="5" t="n">
@@ -32731,7 +32799,7 @@
       </c>
       <c r="AI65" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ65" s="5" t="n">
@@ -32862,7 +32930,7 @@
       </c>
       <c r="AI66" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ66" s="5" t="n">
@@ -32989,7 +33057,7 @@
       </c>
       <c r="AI67" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ67" s="5" t="n">
@@ -33116,7 +33184,7 @@
       </c>
       <c r="AI68" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ68" s="5" t="n">
@@ -33239,7 +33307,7 @@
       </c>
       <c r="AI69" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ69" s="5" t="n">
@@ -33366,7 +33434,7 @@
       </c>
       <c r="AI70" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ70" s="5" t="n">
@@ -33497,7 +33565,7 @@
       </c>
       <c r="AI71" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ71" s="5" t="n">
@@ -33632,7 +33700,7 @@
       </c>
       <c r="AI72" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ72" s="5" t="n">
@@ -33763,7 +33831,7 @@
       </c>
       <c r="AI73" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ73" s="5" t="n">
@@ -33890,7 +33958,7 @@
       </c>
       <c r="AI74" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ74" s="5" t="n">
@@ -34017,7 +34085,7 @@
       </c>
       <c r="AI75" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ75" s="5" t="n">
@@ -34152,7 +34220,7 @@
       </c>
       <c r="AI76" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ76" s="5" t="n">
@@ -34275,7 +34343,7 @@
       </c>
       <c r="AI77" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ77" s="5" t="n">
@@ -36059,11 +36127,11 @@
         <v/>
       </c>
       <c r="M92" s="7" t="n">
-        <v>46409</v>
+        <v>46375</v>
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O92" s="6" t="inlineStr">
@@ -36144,7 +36212,7 @@
       </c>
       <c r="AI92" s="9" t="inlineStr">
         <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ92" s="5" t="n">
@@ -36194,11 +36262,11 @@
         <v/>
       </c>
       <c r="M93" s="7" t="n">
-        <v>46409</v>
+        <v>46375</v>
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>7 months</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O93" s="6" t="inlineStr">
@@ -36275,7 +36343,7 @@
       </c>
       <c r="AI93" s="9" t="inlineStr">
         <is>
-          <t>7 months because Health Choice is the primary payer here (6 months when it is not). Counted in calendar months.</t>
+          <t>Limit as stated: 6 months (not primary) or 7 months (primary). The reference converts months at 30 days, so the real deadline may fall a few days later - count calendar months where it matters.</t>
         </is>
       </c>
       <c r="AJ93" s="5" t="n">
@@ -42176,7 +42244,7 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
@@ -42303,7 +42371,7 @@
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
@@ -42430,7 +42498,7 @@
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
@@ -42565,7 +42633,7 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
@@ -42688,7 +42756,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -42815,7 +42883,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -42942,7 +43010,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -43656,7 +43724,7 @@
       </c>
       <c r="AI26" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
@@ -43783,7 +43851,7 @@
       </c>
       <c r="AI27" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
@@ -44029,7 +44097,7 @@
       </c>
       <c r="AI29" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
@@ -44398,7 +44466,7 @@
       </c>
       <c r="AI32" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
@@ -44519,7 +44587,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI33" s="9" t="n"/>
+      <c r="AI33" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ33" s="5" t="n">
         <v>457</v>
       </c>
@@ -44761,7 +44833,7 @@
       </c>
       <c r="AI35" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ35" s="5" t="n">
@@ -45241,7 +45313,7 @@
       </c>
       <c r="AI39" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ39" s="5" t="n">
@@ -45368,7 +45440,7 @@
       </c>
       <c r="AI40" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ40" s="5" t="n">
@@ -45495,7 +45567,7 @@
       </c>
       <c r="AI41" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ41" s="5" t="n">
@@ -46985,7 +47057,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI53" s="9" t="n"/>
+      <c r="AI53" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ53" s="5" t="n">
         <v>1012</v>
       </c>
@@ -47352,7 +47428,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI56" s="9" t="n"/>
+      <c r="AI56" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ56" s="5" t="n">
         <v>768</v>
       </c>
@@ -47473,7 +47553,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI57" s="9" t="n"/>
+      <c r="AI57" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ57" s="5" t="n">
         <v>769</v>
       </c>
@@ -48201,7 +48285,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="n"/>
+      <c r="AI2" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ2" s="5" t="n">
         <v>580</v>
       </c>
@@ -48802,7 +48890,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -48921,7 +49009,7 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
@@ -49042,7 +49130,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="n"/>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ9" s="5" t="n">
         <v>917</v>
       </c>
@@ -49895,16 +49987,16 @@
         <v/>
       </c>
       <c r="M17" s="7" t="n">
-        <v>46371</v>
+        <v>46311</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P17" s="6" t="n"/>
@@ -49958,7 +50050,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI17" s="9" t="n"/>
+      <c r="AI17" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ17" s="5" t="n">
         <v>527</v>
       </c>
@@ -50006,16 +50102,16 @@
         <v/>
       </c>
       <c r="M18" s="7" t="n">
-        <v>46371</v>
+        <v>46311</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P18" s="6" t="n"/>
@@ -50069,7 +50165,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI18" s="9" t="n"/>
+      <c r="AI18" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ18" s="5" t="n">
         <v>528</v>
       </c>
@@ -50117,16 +50217,16 @@
         <v/>
       </c>
       <c r="M19" s="7" t="n">
-        <v>46371</v>
+        <v>46311</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P19" s="6" t="n"/>
@@ -50180,7 +50280,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI19" s="9" t="n"/>
+      <c r="AI19" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ19" s="5" t="n">
         <v>529</v>
       </c>
@@ -50190,36 +50294,36 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="5" t="n">
-        <v>563006512</v>
+        <v>566543992</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>HF441949223</t>
+          <t>HF552713619</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>AARP United Healthcare</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="K20" s="4" t="n"/>
@@ -50228,16 +50332,16 @@
         <v/>
       </c>
       <c r="M20" s="7" t="n">
-        <v>46540</v>
+        <v>46327</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>150 days</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>MERCY CARE ADVANTAGE</t>
         </is>
       </c>
       <c r="P20" s="6" t="n"/>
@@ -50247,7 +50351,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>1294.23</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="U20" s="8" t="n">
         <v>0</v>
@@ -50255,38 +50359,38 @@
       <c r="V20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="6" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
+      <c r="W20" s="6" t="n"/>
       <c r="X20" s="8" t="n">
-        <v>1294.23</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
-          <t>R609</t>
+          <t>R2243</t>
         </is>
       </c>
       <c r="AA20" s="6" t="inlineStr">
         <is>
-          <t>R2240</t>
-        </is>
-      </c>
-      <c r="AB20" s="6" t="n"/>
+          <t>M79661</t>
+        </is>
+      </c>
+      <c r="AB20" s="6" t="inlineStr">
+        <is>
+          <t>M79662</t>
+        </is>
+      </c>
       <c r="AC20" s="6" t="n"/>
       <c r="AD20" s="5" t="n"/>
       <c r="AE20" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF20" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG20" s="6" t="inlineStr">
@@ -50299,9 +50403,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI20" s="9" t="n"/>
+      <c r="AI20" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 150 days from DOS or eligibility posting, whichever is later.</t>
+        </is>
+      </c>
       <c r="AJ20" s="5" t="n">
-        <v>549</v>
+        <v>969</v>
       </c>
     </row>
     <row r="21">
@@ -50309,36 +50417,36 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="5" t="n">
-        <v>563006512</v>
+        <v>566543992</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>HF441949223</t>
+          <t>HF552713619</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>AARP United Healthcare</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K21" s="4" t="n"/>
@@ -50347,16 +50455,16 @@
         <v/>
       </c>
       <c r="M21" s="7" t="n">
-        <v>46540</v>
+        <v>46327</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>150 days</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>MERCY CARE ADVANTAGE</t>
         </is>
       </c>
       <c r="P21" s="6" t="n"/>
@@ -50366,7 +50474,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="U21" s="8" t="n">
         <v>0</v>
@@ -50374,38 +50482,38 @@
       <c r="V21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="6" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
+      <c r="W21" s="6" t="n"/>
       <c r="X21" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
-          <t>R609</t>
+          <t>R2243</t>
         </is>
       </c>
       <c r="AA21" s="6" t="inlineStr">
         <is>
-          <t>R2240</t>
-        </is>
-      </c>
-      <c r="AB21" s="6" t="n"/>
+          <t>M79661</t>
+        </is>
+      </c>
+      <c r="AB21" s="6" t="inlineStr">
+        <is>
+          <t>M79662</t>
+        </is>
+      </c>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="5" t="n"/>
       <c r="AE21" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF21" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG21" s="6" t="inlineStr">
@@ -50418,9 +50526,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI21" s="9" t="n"/>
+      <c r="AI21" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 150 days from DOS or eligibility posting, whichever is later.</t>
+        </is>
+      </c>
       <c r="AJ21" s="5" t="n">
-        <v>550</v>
+        <v>971</v>
       </c>
     </row>
     <row r="22">
@@ -50428,36 +50540,36 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="5" t="n">
-        <v>563006512</v>
+        <v>566543992</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>HF441949223</t>
+          <t>HF552713619</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>AARP United Healthcare</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K22" s="4" t="n"/>
@@ -50466,16 +50578,16 @@
         <v/>
       </c>
       <c r="M22" s="7" t="n">
-        <v>46540</v>
+        <v>46327</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>150 days</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>MERCY CARE ADVANTAGE</t>
         </is>
       </c>
       <c r="P22" s="6" t="n"/>
@@ -50485,7 +50597,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U22" s="8" t="n">
         <v>0</v>
@@ -50493,38 +50605,38 @@
       <c r="V22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="6" t="inlineStr">
-        <is>
-          <t>06/29/2026</t>
-        </is>
-      </c>
+      <c r="W22" s="6" t="n"/>
       <c r="X22" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
-          <t>R609</t>
+          <t>R2243</t>
         </is>
       </c>
       <c r="AA22" s="6" t="inlineStr">
         <is>
-          <t>R2240</t>
-        </is>
-      </c>
-      <c r="AB22" s="6" t="n"/>
+          <t>M79661</t>
+        </is>
+      </c>
+      <c r="AB22" s="6" t="inlineStr">
+        <is>
+          <t>M79662</t>
+        </is>
+      </c>
       <c r="AC22" s="6" t="n"/>
       <c r="AD22" s="5" t="n"/>
       <c r="AE22" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF22" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG22" s="6" t="inlineStr">
@@ -50537,50 +50649,50 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI22" s="9" t="n"/>
+      <c r="AI22" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 150 days from DOS or eligibility posting, whichever is later.</t>
+        </is>
+      </c>
       <c r="AJ22" s="5" t="n">
-        <v>551</v>
+        <v>999</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="5" t="n">
-        <v>563023730</v>
+        <v>563006512</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>HF544718675</t>
+          <t>HF441949223</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>AARP United Healthcare</t>
-        </is>
-      </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K23" s="4" t="n"/>
@@ -50589,7 +50701,7 @@
         <v/>
       </c>
       <c r="M23" s="7" t="n">
-        <v>46542</v>
+        <v>46540</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -50608,52 +50720,46 @@
         <v>1</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>1438.65</v>
+        <v>0</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>164.45</v>
+        <v>0</v>
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X23" s="8" t="n">
-        <v>46.1</v>
+        <v>1294.23</v>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>M79604</t>
+          <t>R609</t>
         </is>
       </c>
       <c r="AA23" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AB23" s="6" t="inlineStr">
-        <is>
-          <t>R202</t>
-        </is>
-      </c>
+          <t>R2240</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="n"/>
       <c r="AC23" s="6" t="n"/>
-      <c r="AD23" s="5" t="n">
-        <v>566075174</v>
-      </c>
+      <c r="AD23" s="5" t="n"/>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF23" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG23" s="6" t="inlineStr">
@@ -50668,48 +50774,44 @@
       </c>
       <c r="AI23" s="9" t="n"/>
       <c r="AJ23" s="5" t="n">
-        <v>235</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="5" t="n">
-        <v>563023730</v>
+        <v>563006512</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>HF544718675</t>
+          <t>HF441949223</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>AARP United Healthcare</t>
-        </is>
-      </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="K24" s="4" t="n"/>
@@ -50718,7 +50820,7 @@
         <v/>
       </c>
       <c r="M24" s="7" t="n">
-        <v>46542</v>
+        <v>46540</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -50737,52 +50839,46 @@
         <v>1</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>1294.23</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>1164.6</v>
+        <v>0</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>101.25</v>
+        <v>0</v>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X24" s="8" t="n">
-        <v>28.38</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z24" s="6" t="inlineStr">
         <is>
-          <t>M79604</t>
+          <t>R609</t>
         </is>
       </c>
       <c r="AA24" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AB24" s="6" t="inlineStr">
-        <is>
-          <t>R202</t>
-        </is>
-      </c>
+          <t>R2240</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="n"/>
       <c r="AC24" s="6" t="n"/>
-      <c r="AD24" s="5" t="n">
-        <v>566075174</v>
-      </c>
+      <c r="AD24" s="5" t="n"/>
       <c r="AE24" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF24" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG24" s="6" t="inlineStr">
@@ -50797,48 +50893,44 @@
       </c>
       <c r="AI24" s="9" t="n"/>
       <c r="AJ24" s="5" t="n">
-        <v>268</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="5" t="n">
-        <v>563023730</v>
+        <v>563006512</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>HF544718675</t>
+          <t>HF441949223</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Medicare Part B Arizona *</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>AARP United Healthcare</t>
-        </is>
-      </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K25" s="4" t="n"/>
@@ -50847,7 +50939,7 @@
         <v/>
       </c>
       <c r="M25" s="7" t="n">
-        <v>46542</v>
+        <v>46540</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -50866,52 +50958,46 @@
         <v>1</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>785.49</v>
+        <v>0</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>73.08</v>
+        <v>0</v>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X25" s="8" t="n">
-        <v>20.49</v>
+        <v>1649.2</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
-          <t>M79604</t>
+          <t>R609</t>
         </is>
       </c>
       <c r="AA25" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AB25" s="6" t="inlineStr">
-        <is>
-          <t>R202</t>
-        </is>
-      </c>
+          <t>R2240</t>
+        </is>
+      </c>
+      <c r="AB25" s="6" t="n"/>
       <c r="AC25" s="6" t="n"/>
-      <c r="AD25" s="5" t="n">
-        <v>566075174</v>
-      </c>
+      <c r="AD25" s="5" t="n"/>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF25" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG25" s="6" t="inlineStr">
@@ -50926,7 +51012,7 @@
       </c>
       <c r="AI25" s="9" t="n"/>
       <c r="AJ25" s="5" t="n">
-        <v>269</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26">
@@ -50938,11 +51024,11 @@
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="5" t="n">
-        <v>563024734</v>
+        <v>563023730</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>HF364431204</t>
+          <t>HF544718675</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -50952,7 +51038,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -50962,12 +51048,12 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K26" s="4" t="n"/>
@@ -50995,13 +51081,13 @@
         <v>1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>1164.6</v>
+        <v>1438.65</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>101.25</v>
+        <v>164.45</v>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
@@ -51009,21 +51095,29 @@
         </is>
       </c>
       <c r="X26" s="8" t="n">
-        <v>28.38</v>
+        <v>46.1</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>65</v>
       </c>
       <c r="Z26" s="6" t="inlineStr">
         <is>
-          <t>R2241</t>
-        </is>
-      </c>
-      <c r="AA26" s="6" t="n"/>
-      <c r="AB26" s="6" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AA26" s="6" t="inlineStr">
+        <is>
+          <t>M79605</t>
+        </is>
+      </c>
+      <c r="AB26" s="6" t="inlineStr">
+        <is>
+          <t>R202</t>
+        </is>
+      </c>
       <c r="AC26" s="6" t="n"/>
       <c r="AD26" s="5" t="n">
-        <v>566075177</v>
+        <v>566075174</v>
       </c>
       <c r="AE26" s="6" t="inlineStr">
         <is>
@@ -51047,7 +51141,7 @@
       </c>
       <c r="AI26" s="9" t="n"/>
       <c r="AJ26" s="5" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27">
@@ -51059,11 +51153,11 @@
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="5" t="n">
-        <v>563024734</v>
+        <v>563023730</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>HF364431204</t>
+          <t>HF544718675</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -51073,7 +51167,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -51083,12 +51177,12 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K27" s="4" t="n"/>
@@ -51116,13 +51210,13 @@
         <v>1</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>1438.65</v>
+        <v>1164.6</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>164.45</v>
+        <v>101.25</v>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
@@ -51130,21 +51224,29 @@
         </is>
       </c>
       <c r="X27" s="8" t="n">
-        <v>46.1</v>
+        <v>28.38</v>
       </c>
       <c r="Y27" s="5" t="n">
         <v>65</v>
       </c>
       <c r="Z27" s="6" t="inlineStr">
         <is>
-          <t>R2241</t>
-        </is>
-      </c>
-      <c r="AA27" s="6" t="n"/>
-      <c r="AB27" s="6" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>M79605</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="inlineStr">
+        <is>
+          <t>R202</t>
+        </is>
+      </c>
       <c r="AC27" s="6" t="n"/>
       <c r="AD27" s="5" t="n">
-        <v>566075177</v>
+        <v>566075174</v>
       </c>
       <c r="AE27" s="6" t="inlineStr">
         <is>
@@ -51168,7 +51270,7 @@
       </c>
       <c r="AI27" s="9" t="n"/>
       <c r="AJ27" s="5" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28">
@@ -51180,11 +51282,11 @@
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="5" t="n">
-        <v>563024734</v>
+        <v>563023730</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>HF364431204</t>
+          <t>HF544718675</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -51194,7 +51296,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -51204,7 +51306,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -51258,14 +51360,22 @@
       </c>
       <c r="Z28" s="6" t="inlineStr">
         <is>
-          <t>R2241</t>
-        </is>
-      </c>
-      <c r="AA28" s="6" t="n"/>
-      <c r="AB28" s="6" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AA28" s="6" t="inlineStr">
+        <is>
+          <t>M79605</t>
+        </is>
+      </c>
+      <c r="AB28" s="6" t="inlineStr">
+        <is>
+          <t>R202</t>
+        </is>
+      </c>
       <c r="AC28" s="6" t="n"/>
       <c r="AD28" s="5" t="n">
-        <v>566075177</v>
+        <v>566075174</v>
       </c>
       <c r="AE28" s="6" t="inlineStr">
         <is>
@@ -51289,44 +51399,48 @@
       </c>
       <c r="AI28" s="9" t="n"/>
       <c r="AJ28" s="5" t="n">
-        <v>166</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="5" t="n">
-        <v>563068412</v>
+        <v>563024734</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>HF559660036</t>
+          <t>HF364431204</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
+          <t>Bankers Life Colonial Penn Life</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K29" s="4" t="n"/>
@@ -51335,7 +51449,7 @@
         <v/>
       </c>
       <c r="M29" s="7" t="n">
-        <v>46554</v>
+        <v>46542</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
@@ -51354,46 +51468,44 @@
         <v>1</v>
       </c>
       <c r="T29" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1294.23</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0</v>
+        <v>1164.6</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>0</v>
+        <v>101.25</v>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="X29" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>28.38</v>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Z29" s="6" t="inlineStr">
         <is>
-          <t>G549</t>
-        </is>
-      </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>I70213</t>
-        </is>
-      </c>
+          <t>R2241</t>
+        </is>
+      </c>
+      <c r="AA29" s="6" t="n"/>
       <c r="AB29" s="6" t="n"/>
       <c r="AC29" s="6" t="n"/>
-      <c r="AD29" s="5" t="n"/>
+      <c r="AD29" s="5" t="n">
+        <v>566075177</v>
+      </c>
       <c r="AE29" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF29" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG29" s="6" t="inlineStr">
@@ -51408,44 +51520,48 @@
       </c>
       <c r="AI29" s="9" t="n"/>
       <c r="AJ29" s="5" t="n">
-        <v>326</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="5" t="n">
-        <v>563068412</v>
+        <v>563024734</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>HF559660036</t>
+          <t>HF364431204</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
+          <t>Bankers Life Colonial Penn Life</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K30" s="4" t="n"/>
@@ -51454,7 +51570,7 @@
         <v/>
       </c>
       <c r="M30" s="7" t="n">
-        <v>46554</v>
+        <v>46542</v>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
@@ -51473,46 +51589,44 @@
         <v>1</v>
       </c>
       <c r="T30" s="8" t="n">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="U30" s="8" t="n">
-        <v>0</v>
+        <v>1438.65</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>0</v>
+        <v>164.45</v>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="X30" s="8" t="n">
-        <v>1294.23</v>
+        <v>46.1</v>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Z30" s="6" t="inlineStr">
         <is>
-          <t>G549</t>
-        </is>
-      </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>I70213</t>
-        </is>
-      </c>
+          <t>R2241</t>
+        </is>
+      </c>
+      <c r="AA30" s="6" t="n"/>
       <c r="AB30" s="6" t="n"/>
       <c r="AC30" s="6" t="n"/>
-      <c r="AD30" s="5" t="n"/>
+      <c r="AD30" s="5" t="n">
+        <v>566075177</v>
+      </c>
       <c r="AE30" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF30" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG30" s="6" t="inlineStr">
@@ -51527,44 +51641,48 @@
       </c>
       <c r="AI30" s="9" t="n"/>
       <c r="AJ30" s="5" t="n">
-        <v>327</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="5" t="n">
-        <v>563068412</v>
+        <v>563024734</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>HF559660036</t>
+          <t>HF364431204</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
+          <t>Bankers Life Colonial Penn Life</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="K31" s="4" t="n"/>
@@ -51573,7 +51691,7 @@
         <v/>
       </c>
       <c r="M31" s="7" t="n">
-        <v>46554</v>
+        <v>46542</v>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -51592,46 +51710,44 @@
         <v>1</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>1649.2</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>0</v>
+        <v>785.49</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>0</v>
+        <v>73.08</v>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="X31" s="8" t="n">
-        <v>1649.2</v>
+        <v>20.49</v>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Z31" s="6" t="inlineStr">
         <is>
-          <t>G549</t>
-        </is>
-      </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>I70213</t>
-        </is>
-      </c>
+          <t>R2241</t>
+        </is>
+      </c>
+      <c r="AA31" s="6" t="n"/>
       <c r="AB31" s="6" t="n"/>
       <c r="AC31" s="6" t="n"/>
-      <c r="AD31" s="5" t="n"/>
+      <c r="AD31" s="5" t="n">
+        <v>566075177</v>
+      </c>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF31" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG31" s="6" t="inlineStr">
@@ -51646,7 +51762,7 @@
       </c>
       <c r="AI31" s="9" t="n"/>
       <c r="AJ31" s="5" t="n">
-        <v>328</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
@@ -51654,16 +51770,16 @@
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="5" t="n">
-        <v>564058406</v>
+        <v>563068412</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>HF467995431</t>
+          <t>HF559660036</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>06/18/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -51678,12 +51794,12 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>AARP United Healthcare</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="K32" s="4" t="n"/>
@@ -51692,7 +51808,7 @@
         <v/>
       </c>
       <c r="M32" s="7" t="n">
-        <v>46556</v>
+        <v>46554</v>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
@@ -51711,7 +51827,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="8" t="n">
-        <v>1294.23</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="U32" s="8" t="n">
         <v>0</v>
@@ -51721,45 +51837,41 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X32" s="8" t="n">
-        <v>1294.23</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z32" s="6" t="inlineStr">
         <is>
-          <t>I83811</t>
+          <t>G549</t>
         </is>
       </c>
       <c r="AA32" s="6" t="inlineStr">
         <is>
-          <t>I872</t>
-        </is>
-      </c>
-      <c r="AB32" s="6" t="inlineStr">
-        <is>
-          <t>M1711</t>
-        </is>
-      </c>
+          <t>I70213</t>
+        </is>
+      </c>
+      <c r="AB32" s="6" t="n"/>
       <c r="AC32" s="6" t="n"/>
       <c r="AD32" s="5" t="n"/>
       <c r="AE32" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF32" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG32" s="6" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="AH32" s="6" t="inlineStr">
@@ -51769,33 +51881,29 @@
       </c>
       <c r="AI32" s="9" t="n"/>
       <c r="AJ32" s="5" t="n">
-        <v>874</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="5" t="n">
-        <v>564587230</v>
+        <v>563068412</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>HF497148337</t>
+          <t>HF559660036</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>06/23/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -51805,7 +51913,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -51819,7 +51927,7 @@
         <v/>
       </c>
       <c r="M33" s="7" t="n">
-        <v>46561</v>
+        <v>46554</v>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -51841,37 +51949,35 @@
         <v>1294.23</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>1131</v>
+        <v>0</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>127.49</v>
+        <v>0</v>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X33" s="8" t="n">
-        <v>35.74</v>
+        <v>1294.23</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
         <is>
-          <t>I83011</t>
+          <t>G549</t>
         </is>
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>I872</t>
+          <t>I70213</t>
         </is>
       </c>
       <c r="AB33" s="6" t="n"/>
       <c r="AC33" s="6" t="n"/>
-      <c r="AD33" s="5" t="n">
-        <v>567791264</v>
-      </c>
+      <c r="AD33" s="5" t="n"/>
       <c r="AE33" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -51884,7 +51990,7 @@
       </c>
       <c r="AG33" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="AH33" s="6" t="inlineStr">
@@ -51894,33 +52000,29 @@
       </c>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="5" t="n">
-        <v>170</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="5" t="n">
-        <v>564546707</v>
+        <v>563068412</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>HF562069201</t>
+          <t>HF559660036</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -51930,12 +52032,12 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K34" s="4" t="n"/>
@@ -51944,7 +52046,7 @@
         <v/>
       </c>
       <c r="M34" s="7" t="n">
-        <v>46568</v>
+        <v>46554</v>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -51963,44 +52065,38 @@
         <v>1</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>785.49</v>
+        <v>0</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>73.08</v>
+        <v>0</v>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X34" s="8" t="n">
-        <v>20.49</v>
+        <v>1649.2</v>
       </c>
       <c r="Y34" s="5" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="Z34" s="6" t="inlineStr">
         <is>
-          <t>I739</t>
+          <t>G549</t>
         </is>
       </c>
       <c r="AA34" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AB34" s="6" t="inlineStr">
-        <is>
-          <t>M79604</t>
-        </is>
-      </c>
+          <t>I70213</t>
+        </is>
+      </c>
+      <c r="AB34" s="6" t="n"/>
       <c r="AC34" s="6" t="n"/>
-      <c r="AD34" s="5" t="n">
-        <v>567791377</v>
-      </c>
+      <c r="AD34" s="5" t="n"/>
       <c r="AE34" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -52013,7 +52109,7 @@
       </c>
       <c r="AG34" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="AH34" s="6" t="inlineStr">
@@ -52023,33 +52119,29 @@
       </c>
       <c r="AI34" s="9" t="n"/>
       <c r="AJ34" s="5" t="n">
-        <v>74</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="5" t="n">
-        <v>564546707</v>
+        <v>564058406</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>HF562069201</t>
+          <t>HF467995431</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>06/18/2026</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -52059,7 +52151,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -52073,7 +52165,7 @@
         <v/>
       </c>
       <c r="M35" s="7" t="n">
-        <v>46568</v>
+        <v>46556</v>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -52095,54 +52187,52 @@
         <v>1294.23</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>1164.6</v>
+        <v>0</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>101.25</v>
+        <v>0</v>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="X35" s="8" t="n">
-        <v>28.38</v>
+        <v>1294.23</v>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>I739</t>
+          <t>I83811</t>
         </is>
       </c>
       <c r="AA35" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
+          <t>I872</t>
         </is>
       </c>
       <c r="AB35" s="6" t="inlineStr">
         <is>
-          <t>M79604</t>
+          <t>M1711</t>
         </is>
       </c>
       <c r="AC35" s="6" t="n"/>
-      <c r="AD35" s="5" t="n">
-        <v>567791377</v>
-      </c>
+      <c r="AD35" s="5" t="n"/>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF35" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG35" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="AH35" s="6" t="inlineStr">
@@ -52152,7 +52242,7 @@
       </c>
       <c r="AI35" s="9" t="n"/>
       <c r="AJ35" s="5" t="n">
-        <v>75</v>
+        <v>874</v>
       </c>
     </row>
     <row r="36">
@@ -52164,21 +52254,21 @@
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="5" t="n">
-        <v>564546707</v>
+        <v>564587230</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>HF562069201</t>
+          <t>HF497148337</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>06/23/2026</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -52188,12 +52278,12 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K36" s="4" t="n"/>
@@ -52202,7 +52292,7 @@
         <v/>
       </c>
       <c r="M36" s="7" t="n">
-        <v>46568</v>
+        <v>46561</v>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
@@ -52221,13 +52311,13 @@
         <v>1</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>1438.65</v>
+        <v>1131</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>164.45</v>
+        <v>127.49</v>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
@@ -52235,29 +52325,25 @@
         </is>
       </c>
       <c r="X36" s="8" t="n">
-        <v>46.1</v>
+        <v>35.74</v>
       </c>
       <c r="Y36" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>I739</t>
+          <t>I83011</t>
         </is>
       </c>
       <c r="AA36" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AB36" s="6" t="inlineStr">
-        <is>
-          <t>M79604</t>
-        </is>
-      </c>
+          <t>I872</t>
+        </is>
+      </c>
+      <c r="AB36" s="6" t="n"/>
       <c r="AC36" s="6" t="n"/>
       <c r="AD36" s="5" t="n">
-        <v>567791377</v>
+        <v>567791264</v>
       </c>
       <c r="AE36" s="6" t="inlineStr">
         <is>
@@ -52281,49 +52367,43 @@
       </c>
       <c r="AI36" s="9" t="n"/>
       <c r="AJ36" s="5" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Denied</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>46198</v>
-      </c>
+          <t>Finalized</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="5" t="n">
-        <v>563065806</v>
+        <v>564546707</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>HF550504744</t>
+          <t>HF562069201</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -52337,16 +52417,16 @@
         <v/>
       </c>
       <c r="M37" s="7" t="n">
-        <v>46244</v>
+        <v>46568</v>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>DEVOTED</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P37" s="6" t="n"/>
@@ -52359,56 +52439,54 @@
         <v>879.0599999999999</v>
       </c>
       <c r="U37" s="8" t="n">
-        <v>0</v>
+        <v>785.49</v>
       </c>
       <c r="V37" s="8" t="n">
-        <v>0</v>
+        <v>73.08</v>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="X37" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>20.49</v>
       </c>
       <c r="Y37" s="5" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>G5790</t>
+          <t>I739</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
         <is>
-          <t>M5459</t>
+          <t>M79605</t>
         </is>
       </c>
       <c r="AB37" s="6" t="inlineStr">
         <is>
-          <t>M546</t>
-        </is>
-      </c>
-      <c r="AC37" s="6" t="inlineStr">
-        <is>
-          <t>N39498</t>
-        </is>
-      </c>
-      <c r="AD37" s="5" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AC37" s="6" t="n"/>
+      <c r="AD37" s="5" t="n">
+        <v>567791377</v>
+      </c>
       <c r="AE37" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF37" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG37" s="6" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="AH37" s="6" t="inlineStr">
@@ -52418,54 +52496,48 @@
       </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="5" t="n">
-        <v>824</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Denied</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>46198</v>
-      </c>
+          <t>Finalized</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="4" t="n"/>
       <c r="D38" s="5" t="n">
-        <v>563065806</v>
+        <v>564546707</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>HF550504744</t>
+          <t>HF562069201</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K38" s="4" t="n"/>
@@ -52474,16 +52546,16 @@
         <v/>
       </c>
       <c r="M38" s="7" t="n">
-        <v>46244</v>
+        <v>46568</v>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>DEVOTED</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P38" s="6" t="n"/>
@@ -52493,59 +52565,57 @@
         <v>1</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>0</v>
+        <v>1164.6</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>0</v>
+        <v>101.25</v>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="X38" s="8" t="n">
-        <v>1649.2</v>
+        <v>28.38</v>
       </c>
       <c r="Y38" s="5" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>G5790</t>
+          <t>I739</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
         <is>
-          <t>M5459</t>
+          <t>M79605</t>
         </is>
       </c>
       <c r="AB38" s="6" t="inlineStr">
         <is>
-          <t>M546</t>
-        </is>
-      </c>
-      <c r="AC38" s="6" t="inlineStr">
-        <is>
-          <t>N39498</t>
-        </is>
-      </c>
-      <c r="AD38" s="5" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AC38" s="6" t="n"/>
+      <c r="AD38" s="5" t="n">
+        <v>567791377</v>
+      </c>
       <c r="AE38" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF38" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG38" s="6" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="AH38" s="6" t="inlineStr">
@@ -52555,54 +52625,48 @@
       </c>
       <c r="AI38" s="9" t="n"/>
       <c r="AJ38" s="5" t="n">
-        <v>825</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Denied</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>46198</v>
-      </c>
+          <t>Finalized</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="4" t="n"/>
       <c r="D39" s="5" t="n">
-        <v>563065806</v>
+        <v>564546707</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>HF550504744</t>
+          <t>HF562069201</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Devoted Health Plan</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K39" s="4" t="n"/>
@@ -52611,16 +52675,16 @@
         <v/>
       </c>
       <c r="M39" s="7" t="n">
-        <v>46244</v>
+        <v>46568</v>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>DEVOTED</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P39" s="6" t="n"/>
@@ -52630,59 +52694,57 @@
         <v>1</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>0</v>
+        <v>1438.65</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>0</v>
+        <v>164.45</v>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>06/29/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="X39" s="8" t="n">
-        <v>1294.23</v>
+        <v>46.1</v>
       </c>
       <c r="Y39" s="5" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
         <is>
-          <t>G5790</t>
+          <t>I739</t>
         </is>
       </c>
       <c r="AA39" s="6" t="inlineStr">
         <is>
-          <t>M5459</t>
+          <t>M79605</t>
         </is>
       </c>
       <c r="AB39" s="6" t="inlineStr">
         <is>
-          <t>M546</t>
-        </is>
-      </c>
-      <c r="AC39" s="6" t="inlineStr">
-        <is>
-          <t>N39498</t>
-        </is>
-      </c>
-      <c r="AD39" s="5" t="n"/>
+          <t>M79604</t>
+        </is>
+      </c>
+      <c r="AC39" s="6" t="n"/>
+      <c r="AD39" s="5" t="n">
+        <v>567791377</v>
+      </c>
       <c r="AE39" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF39" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG39" s="6" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="AH39" s="6" t="inlineStr">
@@ -52692,34 +52754,44 @@
       </c>
       <c r="AI39" s="9" t="n"/>
       <c r="AJ39" s="5" t="n">
-        <v>826</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="4" t="n"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>46198</v>
+      </c>
       <c r="D40" s="5" t="n">
-        <v>563009396</v>
+        <v>563065806</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>HF449340318</t>
+          <t>HF550504744</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>UMR Wausau / UHIS</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>UMR Wausau / UHIS</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -52729,7 +52801,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="K40" s="4" t="n"/>
@@ -52737,11 +52809,17 @@
         <f>IF($M40="","",$M40-TODAY())</f>
         <v/>
       </c>
-      <c r="M40" s="7" t="n"/>
-      <c r="N40" s="6" t="n"/>
+      <c r="M40" s="7" t="n">
+        <v>46244</v>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>60 days</t>
+        </is>
+      </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>UMR / WAUSAU</t>
+          <t>DEVOTED</t>
         </is>
       </c>
       <c r="P40" s="6" t="n"/>
@@ -52751,7 +52829,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>1649.2</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="U40" s="8" t="n">
         <v>0</v>
@@ -52761,40 +52839,44 @@
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>07/17/2026</t>
+          <t>06/29/2026</t>
         </is>
       </c>
       <c r="X40" s="8" t="n">
-        <v>1649.2</v>
+        <v>879.0599999999999</v>
       </c>
       <c r="Y40" s="5" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="Z40" s="6" t="inlineStr">
         <is>
-          <t>R609</t>
+          <t>G5790</t>
         </is>
       </c>
       <c r="AA40" s="6" t="inlineStr">
         <is>
-          <t>M79604</t>
+          <t>M5459</t>
         </is>
       </c>
       <c r="AB40" s="6" t="inlineStr">
         <is>
-          <t>M79605</t>
-        </is>
-      </c>
-      <c r="AC40" s="6" t="n"/>
+          <t>M546</t>
+        </is>
+      </c>
+      <c r="AC40" s="6" t="inlineStr">
+        <is>
+          <t>N39498</t>
+        </is>
+      </c>
       <c r="AD40" s="5" t="n"/>
       <c r="AE40" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF40" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Surprise - Reems</t>
+          <t>ASAP - DEER VALLEY 240</t>
         </is>
       </c>
       <c r="AG40" s="6" t="inlineStr">
@@ -52809,34 +52891,44 @@
       </c>
       <c r="AI40" s="9" t="n"/>
       <c r="AJ40" s="5" t="n">
-        <v>478</v>
+        <v>824</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="4" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>46198</v>
+      </c>
       <c r="D41" s="5" t="n">
-        <v>566543992</v>
+        <v>563065806</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>HF552713619</t>
+          <t>HF550504744</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -52846,7 +52938,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K41" s="4" t="n"/>
@@ -52854,11 +52946,17 @@
         <f>IF($M41="","",$M41-TODAY())</f>
         <v/>
       </c>
-      <c r="M41" s="7" t="n"/>
-      <c r="N41" s="6" t="n"/>
+      <c r="M41" s="7" t="n">
+        <v>46244</v>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>60 days</t>
+        </is>
+      </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>MERCY CARE ADVANTAGE</t>
+          <t>DEVOTED</t>
         </is>
       </c>
       <c r="P41" s="6" t="n"/>
@@ -52868,7 +52966,7 @@
         <v>1</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="U41" s="8" t="n">
         <v>0</v>
@@ -52876,29 +52974,37 @@
       <c r="V41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="6" t="n"/>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
       <c r="X41" s="8" t="n">
-        <v>879.0599999999999</v>
+        <v>1649.2</v>
       </c>
       <c r="Y41" s="5" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
         <is>
-          <t>R2243</t>
+          <t>G5790</t>
         </is>
       </c>
       <c r="AA41" s="6" t="inlineStr">
         <is>
-          <t>M79661</t>
+          <t>M5459</t>
         </is>
       </c>
       <c r="AB41" s="6" t="inlineStr">
         <is>
-          <t>M79662</t>
-        </is>
-      </c>
-      <c r="AC41" s="6" t="n"/>
+          <t>M546</t>
+        </is>
+      </c>
+      <c r="AC41" s="6" t="inlineStr">
+        <is>
+          <t>N39498</t>
+        </is>
+      </c>
       <c r="AD41" s="5" t="n"/>
       <c r="AE41" s="6" t="inlineStr">
         <is>
@@ -52922,34 +53028,44 @@
       </c>
       <c r="AI41" s="9" t="n"/>
       <c r="AJ41" s="5" t="n">
-        <v>969</v>
+        <v>825</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="4" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>46198</v>
+      </c>
       <c r="D42" s="5" t="n">
-        <v>566543992</v>
+        <v>563065806</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>HF552713619</t>
+          <t>HF550504744</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>Devoted Health Plan</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -52959,7 +53075,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="K42" s="4" t="n"/>
@@ -52967,11 +53083,17 @@
         <f>IF($M42="","",$M42-TODAY())</f>
         <v/>
       </c>
-      <c r="M42" s="7" t="n"/>
-      <c r="N42" s="6" t="n"/>
+      <c r="M42" s="7" t="n">
+        <v>46244</v>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>60 days</t>
+        </is>
+      </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>MERCY CARE ADVANTAGE</t>
+          <t>DEVOTED</t>
         </is>
       </c>
       <c r="P42" s="6" t="n"/>
@@ -52981,7 +53103,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="U42" s="8" t="n">
         <v>0</v>
@@ -52989,29 +53111,37 @@
       <c r="V42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="6" t="n"/>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026</t>
+        </is>
+      </c>
       <c r="X42" s="8" t="n">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="Y42" s="5" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Z42" s="6" t="inlineStr">
         <is>
-          <t>R2243</t>
+          <t>G5790</t>
         </is>
       </c>
       <c r="AA42" s="6" t="inlineStr">
         <is>
-          <t>M79661</t>
+          <t>M5459</t>
         </is>
       </c>
       <c r="AB42" s="6" t="inlineStr">
         <is>
-          <t>M79662</t>
-        </is>
-      </c>
-      <c r="AC42" s="6" t="n"/>
+          <t>M546</t>
+        </is>
+      </c>
+      <c r="AC42" s="6" t="inlineStr">
+        <is>
+          <t>N39498</t>
+        </is>
+      </c>
       <c r="AD42" s="5" t="n"/>
       <c r="AE42" s="6" t="inlineStr">
         <is>
@@ -53035,7 +53165,7 @@
       </c>
       <c r="AI42" s="9" t="n"/>
       <c r="AJ42" s="5" t="n">
-        <v>971</v>
+        <v>826</v>
       </c>
     </row>
     <row r="43">
@@ -53043,26 +53173,26 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="5" t="n">
-        <v>566543992</v>
+        <v>563009396</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>HF552713619</t>
+          <t>HF449340318</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>UMR Wausau / UHIS</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>UMR Wausau / UHIS</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -53072,7 +53202,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="K43" s="4" t="n"/>
@@ -53084,7 +53214,7 @@
       <c r="N43" s="6" t="n"/>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>MERCY CARE ADVANTAGE</t>
+          <t>UMR / WAUSAU</t>
         </is>
       </c>
       <c r="P43" s="6" t="n"/>
@@ -53094,7 +53224,7 @@
         <v>1</v>
       </c>
       <c r="T43" s="8" t="n">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="U43" s="8" t="n">
         <v>0</v>
@@ -53102,38 +53232,42 @@
       <c r="V43" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="6" t="n"/>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
       <c r="X43" s="8" t="n">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="Y43" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z43" s="6" t="inlineStr">
         <is>
-          <t>R2243</t>
+          <t>R609</t>
         </is>
       </c>
       <c r="AA43" s="6" t="inlineStr">
         <is>
-          <t>M79661</t>
+          <t>M79604</t>
         </is>
       </c>
       <c r="AB43" s="6" t="inlineStr">
         <is>
-          <t>M79662</t>
+          <t>M79605</t>
         </is>
       </c>
       <c r="AC43" s="6" t="n"/>
       <c r="AD43" s="5" t="n"/>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF43" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY 240</t>
+          <t>ASAP - Surprise - Reems</t>
         </is>
       </c>
       <c r="AG43" s="6" t="inlineStr">
@@ -53146,9 +53280,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI43" s="9" t="n"/>
+      <c r="AI43" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ43" s="5" t="n">
-        <v>999</v>
+        <v>478</v>
       </c>
     </row>
     <row r="44">
@@ -53481,7 +53619,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI46" s="9" t="n"/>
+      <c r="AI46" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ46" s="5" t="n">
         <v>906</v>
       </c>
@@ -53586,7 +53728,7 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 - Due in 31+ days: 284</t>
+          <t xml:space="preserve">    3 - Due in 31+ days: 287</t>
         </is>
       </c>
     </row>
@@ -53600,7 +53742,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 - No limit on file: 42</t>
+          <t xml:space="preserve">    5 - No limit on file: 39</t>
         </is>
       </c>
     </row>

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -53664,7 +53663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -53804,7 +53803,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -53821,46 +53820,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
